--- a/artfynd/A 38465-2026 artfynd.xlsx
+++ b/artfynd/A 38465-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136347720</v>
       </c>
       <c r="B2" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38465-2026 artfynd.xlsx
+++ b/artfynd/A 38465-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136347720</v>
       </c>
       <c r="B2" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38465-2026 artfynd.xlsx
+++ b/artfynd/A 38465-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136347720</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38465-2026 artfynd.xlsx
+++ b/artfynd/A 38465-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136347720</v>
       </c>
       <c r="B2" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38465-2026 artfynd.xlsx
+++ b/artfynd/A 38465-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136347720</v>
       </c>
       <c r="B2" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
